--- a/TRIAGE_1910.xlsx
+++ b/TRIAGE_1910.xlsx
@@ -8,24 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабель (ЭОМ)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Соль" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Форма снаряжение" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СИЗ (респираторы)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сантехника арматура" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Одежда СИЗ" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СС видеонаблюдение" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вентиляция фильтры" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медрасходники (пробирки)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кабель (ЭОМ)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Соль" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Форма снаряжение" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СИЗ (респираторы)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сантехника арматура" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Одежда СИЗ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СС видеонаблюдение" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вентиляция фильтры" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кабель (ЭОМ)'!$A$1:$N$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Соль'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Форма снаряжение'!$A$1:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'СИЗ (респираторы)'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Сантехника арматура'!$A$1:$N$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Одежда СИЗ'!$A$1:$N$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'СС видеонаблюдение'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Вентиляция фильтры'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Медрасходники (пробирки)'!$A$1:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Кабель (ЭОМ)'!$A$1:$N$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Соль'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Форма снаряжение'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'СИЗ (респираторы)'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Сантехника арматура'!$A$1:$N$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Одежда СИЗ'!$A$1:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'СС видеонаблюдение'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Вентиляция фильтры'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -563,194 +565,194 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Медрасходники (пробирки)</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>267068719.83</v>
+        <v>29777435.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>267068719.83</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1001200</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Форма/снаряжение</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>22968701.7</v>
+        <v>1001200</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>СИЗ (респираторы)</t>
+          <t>Форма/снаряжение</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1461588.15</v>
+        <v>22968701.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Сантехника/арматура</t>
+          <t>СИЗ (респираторы)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1822120872.15</v>
+        <v>1461588.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ</t>
+          <t>Сантехника/арматура</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>209646638.74</v>
+        <v>1822120872.15</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>СС/видеонаблюдение</t>
+          <t>Одежда/СИЗ</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>209646638.74</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1757605.78</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>8</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -759,28 +761,56 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>СС/видеонаблюдение</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1757605.78</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Вентиляция/фильтры</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,7 +820,5299 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Номер закупки</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Регион</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Закон</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Способ</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Площадка</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>НМЦК, ₽</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Окончание подачи</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>СМП</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Обеспечение заявки</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Обеспечение контракта</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Аванс</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>386-176</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Поставка фильтров (абсолютной очистки, карманных), отсрочка 60 календарных дней, Российская Федерация, Новосибирская область, муниципальный округ Маслянинский, квартал Молочный, земельный участок 1.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>ООО «ЭкоНива-Семена»</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>36 Воронежская область</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="n">
+        <v>46315.5</v>
+      </c>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>0321500000226000310</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>поставка товара для обеспечения нужд Ставропольского края</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Ставропольского Края «Ставропольский Краевой Клинический Перинатальный Центр № 1»</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n">
+        <v>46318.79166666666</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>4646700</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Поставка фильтров (топливных, воздушных, масляных)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Лукойл-Транс»</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="10" t="n">
+        <v>46332.5</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Номер закупки</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Регион</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Закон</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Способ</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Площадка</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>НМЦК, ₽</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Окончание подачи</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>СМП</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Обеспечение заявки</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Обеспечение контракта</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Аванс</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>0373200087826001918</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания и разделительным гелем для нужд ГБУЗ "ММКЦ "Коммунарка" ДЗМ" (Лот 2)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ г. Москвы «Московский Многопрофильный Клинический Центр «Коммунарка» Департамента Здравоохранения Города Москвы»</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>2999680</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>46317.375</v>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>14998.4</v>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>0373200011426001679</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Поставка контейнеров с поршнем для мочи (заявка 428-зк, лот 3)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ г. Москвы «Городская Клиническая Больница № 67 Имени Л. А. Ворохобова Департамента Здравоохранения Города Москвы»</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>2389196.8</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>46317.41666666666</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>11945.98</v>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>0338200002226000430</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинский изделий (Пробирки вакуумные)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>41 Камчатский край</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>2221608</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>46318.16666666666</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="6" t="n">
+        <v>22216.08</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>111080.4</v>
+      </c>
+      <c r="N4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>32616459808</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>270040144 «Товары канцелярские» для нужд филиала «Кировский» ПАО «Т Плюс» в 2027 году (4636973)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ПАО «Т Плюс»</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Закупка иного способа размещения</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>ПАО «Т‑Плюс»</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>1788618.09</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>46317.58333333334</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>4636973</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>270040144 «Товары канцелярские» для нужд филиала «Кировский» ПАО «Т Плюс» в 2027 году</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Филиал «Кировский» ПАО «Т Плюс»</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>1788618.09</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>46317.58333333334</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>339454</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Поставка стоматологических материалов</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Частное учреждение Здравоохранения «Клиническая Больница «Ржд-Медицина» Города Санкт-Петербурга»</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>РЖД-Медицина</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>1777231.3</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>46316.5</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>32616468993</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Поставка реагентов для анализатора электролитов AVL 9180 имеющегося в наличии и используемого Заказчиком</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Государственное автономное учреждение Здравоохранения Свердловской обл. «Свердловский Областной Клинический Госпиталь Для Ветеранов Войн Имени С.И. Спектора»</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>66 Свердловская область</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>1706950</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>46316.29166666666</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr"/>
+      <c r="M8" s="6" t="n">
+        <v>34139</v>
+      </c>
+      <c r="N8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>0387200029826000347</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных для взятия образцов крови (1)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Нижневартовская Окружная Клиническая Больница»</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>46315.29166666666</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>0815500000526012916</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Чувашской Республики «Больница Скорой Медицинской Помощи» Министерства Здравоохранения Чувашской Республики</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>21 Чувашская республика</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>1474800</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>46317.375</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr"/>
+      <c r="L10" s="6" t="n">
+        <v>7374</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>73740</v>
+      </c>
+      <c r="N10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>332598</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных медицинских материалов</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Частное учреждение Здравоохранения «Клиническая Больница «Ржд-Медицина» Города Минеральные Воды»</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>РЖД-Медицина</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>1034883</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>46582.41666666666</v>
+      </c>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>0873200009826004941</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме на поставку медицинского изделия ВИЧ - инфекции (МИ2026-314)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ГКУ г. Москвы «Агентство по Закупкам (Контрактная Служба) Департамента Здравоохранения Города Москвы»</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>1034250</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>46315.375</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="6" t="n">
+        <v>5171.25</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>51712.5</v>
+      </c>
+      <c r="N12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>32616460692</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Поставка канцелярских товаров</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Вторресурсхолдинг»</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Закупка иного способа размещения</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>46323.41666666666</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
+      <c r="N13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>0815500000526013001</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>поставка медицинских изделий - пробирки для взятия образцов крови (часть 2)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Чувашской Республики «Новочебоксарская Городская Больница» Министерства Здравоохранения Чувашской Республики</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>21 Чувашская республика</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>947814</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>46318.375</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>0372200263426001564</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Поставка изделий медицинского назначения</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>СПБ ГБУЗ «Городская Александровская больница»</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>863700</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>46318.33333333334</v>
+      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="6" t="n">
+        <v>86370</v>
+      </c>
+      <c r="N15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>0373100014426000179</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных для взятия образцов крови на 2027 год</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>ГКУ «Центральная поликлиника Фтс России»</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>662120</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>46317.41666666666</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>10.00 %</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>32616478499</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Поставка "Канцелярские товары" для нужд филиала "Нижегородский" ПАО "Т Плюс"</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>ПАО «Т Плюс»</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Конкурс в электронной форме</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>644005.45</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>46321.5</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>0318300596226000122</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (пробирки для забора крови)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>46318.41666666666</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>32616477300</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Поставка товара медицинского назначения (пробирки)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Государственное автономное учреждение Здравоохранения Тюменской обл. «Городская Поликлиника №13»</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>72 Тюменская область</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>499500</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>46318.29166666666</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>0325300007726000124</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для КДЛ (пробирки лот 2)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Астраханской обл. «Городская поликлиника №5»</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>30 Астраханская область</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>496200</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>46321.33333333334</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr"/>
+      <c r="M20" s="6" t="n">
+        <v>24810</v>
+      </c>
+      <c r="N20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>10761439</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Поставка хозяйственных товаров</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>МАУ Культуры Городского Округа «Город Калининград» «Калининградский Зоопарк»</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>475213.35</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>46318.5</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>32616470311</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Поставка канцелярских товаров</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>МАОУ СОШ № 96 г. Тюмени</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>72 Тюменская область</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Закупка иного способа размещения</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП МИР</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>463475.6</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>46317.25</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
+      <c r="N22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>10772811</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Выкашивание газонов партерных и обыкновенных моторной косилкой (ул. Крупской, контейнерные площадки, Троицкая, Попкова (сквер), Рабочая, Подгорная, Попкова, Администрация района, Ленина, Калинина, остановки по городу)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Администрация Бутурлиновского городского поселения Бутурлиновского муниципального района Воронежской обл.</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>36 Воронежская область</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>379194</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>46316.54166666666</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>0815500000526013075</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>поставка медицинских изделий - пробирки для взятия образцов крови (часть 1)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Чувашской Республики «Новочебоксарская Городская Больница» Министерства Здравоохранения Чувашской Республики</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>21 Чувашская республика</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>299004</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>46321.375</v>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>32616476298</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Запрос оферт в электронном магазине на право заключения договора на поставку канцелярских товаров для нужд Аппарата управления филиала ФГУП "ГРЧЦ" в ЮСКФО</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Филиал ФГУП «Грчц» в Южном и Северо-Кавказском Федеральных Округах</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Запрос оферт</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>259651.45</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>46318.41666666666</v>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>0318200081326000039</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Поставка изделий медицинского назначения (контейнеров для сбора проб)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Бюро судебно-медицинской экспертизы № 2» министерства здравоохранения Краснодарского края</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>247273</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>46321.33333333334</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>0368300009626000124</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Расходные материалы для лаборатории (пробирки вакуумные для взятия образцов крови ИВД)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>ГУЧ Здравоохранения «Чердаклинская Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>73 Ульяновская область</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>181920</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>46315.375</v>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>0813500000126018988</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>зз-0014-43811 - 2026 Поставка пробирки вакуумной для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Удмуртской Республики «Игринская Межрайонная Станция по Борьбе с Болезнями Животных»</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>18 Удмуртская республика</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>ZakazRF (АГЗРТ)</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>46315.25</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>0333300001226000124</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий: пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Областное бюджетное учреждение здравоохранения «Родильный дом № 4»</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>37 Ивановская область</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>174232</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>46315.33333333334</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>3770402</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцовкрови ИВД, с активаторомсвертывания/разделительным гелем, 6 мл</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Московской обл. «Бюро судебно-медицинской экспертизы»</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Электронный магазин Московской области</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>168070</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>46315.43125</v>
+      </c>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>6252040</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцовкрови ИВД, с активаторомсвертывания/разделительным гелем, 6 мл</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Московской обл. «Бюро судебно-медицинской экспертизы»</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Портал поставщиков</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>168070</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>46315.43125</v>
+      </c>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>10765864</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцовкрови ИВД, с активаторомсвертывания/разделительным гелем, 6 мл</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Московской обл. «Бюро судебно-медицинской экспертизы»</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>168070</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>46315.43125</v>
+      </c>
+      <c r="K32" s="8" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
+      <c r="N32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>0361200003026000078</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных для взятия крови</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Сахалинский областной центр по профилактике и борьбе со СПИДом»</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>65 Сахалинская область</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>167232</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>46318.04166666666</v>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>10.00 %</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>0372200087126000051</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (пробирки вакуумные)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>СПБ ГБУЗ «Городская поликлиника № 72»</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Сбербанк-АСТ</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>164060</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>46316.29166666666</v>
+      </c>
+      <c r="K34" s="8" t="inlineStr"/>
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="6" t="n">
+        <v>8203</v>
+      </c>
+      <c r="N34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>0813500000126019336</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>зз-0014-44145 - 2026 Пробирка вакуумная для взятия образцов крови ИВД</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Здравоохранения Удмуртской Республики «Республиканский Клинический Центр Психического Здоровья Министерства Здравоохранения Удмуртской Республики»</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>18 Удмуртская республика</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>ZakazRF (АГЗРТ)</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>149280</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>46317.25</v>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>5.00 %</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>0829500001126006763</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для лаборатории (пробирки)</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>ГУЧ здравоохранения «Больница № 16»</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>34 Волгоградская область</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>111800</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>46315.29166666666</v>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
+      <c r="N36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>10731867</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>на поставку изделий медицинского назначения для нужд Государственного бюджетного учреждения здравоохранения "Онкологический центр Калининградской области"</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Онкологический Центр Калининградской Области»</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>104898.65</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>46325.75763888889</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
+      <c r="N37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>32616455248</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Поставка контейнеров для сбора проб биоматериала</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Государственное автономное учреждение Здравоохранения Свердловской обл. «Свердловская Областная Клиническая Психиатрическая Больница»</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>66 Свердловская область</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>РАД (Lot-Online)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>103205</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>46315.20833333334</v>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
+      <c r="N38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>6253789</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для отделения медицинских осмотров</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Киселевская Городская Больница»</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>42 Кемеровская область</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Портал поставщиков</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>83000</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>46315.44097222222</v>
+      </c>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
+      <c r="N39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>2040559</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Поставка канцелярских и хозяйственных товаров на 4 квартал 2026 года.</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Специализированное ГБУ Волгоградской обл. «Арчединское Лесничество»</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>34 Волгоградская область</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>OTC-tender</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>59365.9</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>46315.33333333334</v>
+      </c>
+      <c r="K40" s="8" t="inlineStr"/>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
+      <c r="N40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>339182</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных медицинских материалов для лабораторных исследований для нужд ЧУЗ ОАО "РЖД"</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Частное учреждение Здравоохранения «Клиническая Больница «Ржд-Медицина» Города Барнаул»</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>22 Алтайский край</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>РЖД-Медицина</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>54080.19</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>46317.25</v>
+      </c>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1015936</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Поставка офисных принадлежностей (52-ТД-2027-ЦЗ-ОМТК)</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Теплоснабжающая компания Мосэнерго»</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>47304.07</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>46317.375</v>
+      </c>
+      <c r="K42" s="8" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
+      <c r="N42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>5000032600062</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Поставка канцелярских товаров</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>МКУ Вологодского Муниципального Округа «Расчетно-Аналитический Центр»</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>35 Вологодская область</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Закупки Вологодской области</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>43847.86</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>46315.33333333334</v>
+      </c>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="6" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>32616471325</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания, красная крышка 6мл</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Республики Крым «Евпаторийский Городской Ветеринарный Лечебно-Профилактический Центр»</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>91 Республика Крым</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Закупка иного способа размещения</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>31600</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>46316.375</v>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
+      <c r="N44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>32616470672</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских расходных материалов (контейнеры)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Ленинградской обл. «Центр Профессиональной Патологии»</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>47 Ленинградская область</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>30900</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>46316.375</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Для СМП, СОНО</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="6" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>2038050</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Поставка хозяйственных товаров</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Муниципальное бюджетное Общеобразовательное учреждение Городского Округа Тольятти «Школа № 15 Имени Героя Советского Союза Викторова Константина Николаевича»</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>63 Самарская область</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>OTC-tender</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>24747.4</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K46" s="8" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
+      <c r="N46" s="6" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>100304268126100100</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Расходные материалы медицинского назначения</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Федеральное казенное учреждение Здравоохранения «Медико-Санитарная Часть № 31 Федеральной Службы Исполнения Наказаний»</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>31 Белгородская область</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>ЕАТ (Березка)</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>46315.45069444444</v>
+      </c>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>ИМЗ-2026-044445</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с K2ЭДТА</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Ветеринарная Станция Туймазинского Района и г. Октябрьского Республики Башкортостан</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>02 Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Агрегатор торгов малого объема</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>2766</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>46316.44444444445</v>
+      </c>
+      <c r="K48" s="8" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr"/>
+      <c r="N48" s="6" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>384-296</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>32112 Аутсорсинг по производству Русагро-Аткарск</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Группа Компаний «Русагро»</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>31 Белгородская область</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="10" t="n">
+        <v>46318</v>
+      </c>
+      <c r="K49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr"/>
+      <c r="M49" s="8" t="inlineStr"/>
+      <c r="N49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>0373100120526000713</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>НИИ Урологии и Интервенционной Радиологии им. Н.А. Лопаткина - Филиал Федерального Государственного Бюджетного Учреждения «Национальный Медицинский Исследовательский Центр Радиологии» Министерства Здравоохранения РФ</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>40 Калужская область</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="10" t="n">
+        <v>46315.66666666666</v>
+      </c>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
+      <c r="N50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>0373100120526000714</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>НИИ Урологии и Интервенционной Радиологии им. Н.А. Лопаткина - Филиал Федерального Государственного Бюджетного Учреждения «Национальный Медицинский Исследовательский Центр Радиологии» Министерства Здравоохранения РФ</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>40 Калужская область</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="10" t="n">
+        <v>46315.66666666666</v>
+      </c>
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr"/>
+      <c r="M51" s="8" t="inlineStr"/>
+      <c r="N51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>0318200047826000729</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий : пробирка вакуумная для взятия образцов крови ИВД, с натрия цитратом; пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания; пробирка вакуумная для взятия образцов крови ИВД, с K3ЭДТА.</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Специализированная Психиатрическая Больница № 7» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="10" t="n">
+        <v>46321.45833333334</v>
+      </c>
+      <c r="K52" s="8" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr"/>
+      <c r="N52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>0358300219726000085</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Поставка ИМН для лаборатории</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Ростовской обл. «Городская Поликлиника №9» в г.Ростове-на-Дону</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>61 Ростовская область</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="10" t="n">
+        <v>46317.41666666666</v>
+      </c>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr"/>
+      <c r="M53" s="8" t="inlineStr"/>
+      <c r="N53" s="6" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>0321200022326000125</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>поставка в 2027 году пробирок вакуумных для взятия образцов крови</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Ставропольского Края «Ставропольская Краевая Станция Переливания Крови»</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="10" t="n">
+        <v>46318.99930555555</v>
+      </c>
+      <c r="K54" s="8" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr"/>
+      <c r="N54" s="6" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>0367200003426000267</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>поставка медицинских изделий: Пробирки вакуумные</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Тюменской обл. «Областной Клинический Фтизиопульмонологический Центр»</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>72 Тюменская область</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="10" t="n">
+        <v>46325.41666666666</v>
+      </c>
+      <c r="K55" s="8" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr"/>
+      <c r="M55" s="8" t="inlineStr"/>
+      <c r="N55" s="6" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>0372200258526000807</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий (пробирок вакуумных) в 2027 году</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>СПБ ГБУЗ «Городская Больница Святого Великомученика Георгия»</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="10" t="n">
+        <v>46315.375</v>
+      </c>
+      <c r="K56" s="8" t="inlineStr"/>
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+      <c r="N56" s="6" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>0318300026126000031</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок для забора биологического материала пациентам ГБУЗ "Новопокровская ЦРБ" МЗ КК</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Новопокровская Центральная Районная Больница» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="10" t="n">
+        <v>46316.41666666666</v>
+      </c>
+      <c r="K57" s="8" t="inlineStr"/>
+      <c r="L57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
+      <c r="N57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>0318300596226000094</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>поставка пробирок</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="10" t="n">
+        <v>46315.375</v>
+      </c>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="6" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>0334500004426000223</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Поставка Пробирок вакуумных для взятия образцов крови</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Областное ГБУЗ «Усть-Илимская Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="10" t="n">
+        <v>46316.625</v>
+      </c>
+      <c r="K59" s="8" t="inlineStr"/>
+      <c r="L59" s="8" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="6" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1025681</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>СПБ государственное бюджетное Стационарное учреждение Социального Обслуживания Населения «Дом Социального Обслуживания «Стрельна»</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>78 Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K60" s="8" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
+      <c r="N60" s="6" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>0355300013926000041</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для клинико-диагностической лаборатории</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Бессоновская Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>58 Пензенская область</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="10" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="K61" s="8" t="inlineStr"/>
+      <c r="L61" s="8" t="inlineStr"/>
+      <c r="M61" s="8" t="inlineStr"/>
+      <c r="N61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>0367100021326000069</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Приобретение расходных материалов в рамках программы «Экспорт продукции АПК»</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Управление Федеральной Службы по Ветеринарному и Фитосанитарному Надзору по Тюменской обл.,Ямало-Ненецкому и Ханты-Мансийскому Автономным Округам</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>72 Тюменская область</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="10" t="n">
+        <v>46318.58333333334</v>
+      </c>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>0318300173926000121</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Изделия медицинского назначения (пробирки вакуумные)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Городская Клиническая Больница № 3 Города Краснодара» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="10" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="6" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>0348100068726000680</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Закупка расходных материалов для лаборатории</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>ФГКУ «Главный Клинический Военный Госпиталь»</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>50 Московская область</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="n"/>
+      <c r="J64" s="10" t="n">
+        <v>46315.33333333334</v>
+      </c>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
+      <c r="N64" s="6" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1024840</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная с активатором свертывания, красная крышка 6мл</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Республики Крым «Евпаторийский Городской Ветеринарный Лечебно-Профилактический Центр»</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>91 Республика Крым</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="10" t="n">
+        <v>46316.375</v>
+      </c>
+      <c r="K65" s="8" t="inlineStr"/>
+      <c r="L65" s="8" t="inlineStr"/>
+      <c r="M65" s="8" t="inlineStr"/>
+      <c r="N65" s="6" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>0334300104526000106</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Поставка контейнеров для сбора кала, контейнеров для сбора мочи</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Областное ГБУЗ «Братская Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="10" t="n">
+        <v>46316.54166666666</v>
+      </c>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
+      <c r="N66" s="6" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1025113</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Поставка вакуумных пробирок</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Медсервис»</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>02 Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="10" t="n">
+        <v>46315.29166666666</v>
+      </c>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="inlineStr"/>
+      <c r="M67" s="8" t="inlineStr"/>
+      <c r="N67" s="6" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>0334300108426000030</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>поставка товара (Пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания; КТРУ 32.50.50.000-00001454)</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Областное ГБУЗ «Иркутская Городская Поликлиника № 11»</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>38 Иркутская область</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="10" t="n">
+        <v>46316.125</v>
+      </c>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr"/>
+      <c r="N68" s="6" t="n"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>0322200015226001208</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Краевое ГБУЗ «Краевой Клинический Центр Онкологии» Министерства Здравоохранения Хабаровского Края</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>27 Хабаровский край</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="10" t="n">
+        <v>46316.18125</v>
+      </c>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr"/>
+      <c r="M69" s="8" t="inlineStr"/>
+      <c r="N69" s="6" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>0322300036726000233</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Краевое ГБУЗ «Городская Поликлиника Железнодорожного Района» Министерства Здравоохранения Хабаровского Края</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>27 Хабаровский край</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="10" t="n">
+        <v>46315.45833333334</v>
+      </c>
+      <c r="K70" s="8" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
+      <c r="N70" s="6" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1025512</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Ставропольского края «Ипатовская районная станция по борьбе с болезнями животных»</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="n"/>
+      <c r="J71" s="10" t="n">
+        <v>46316.70833333334</v>
+      </c>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1026776</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Ставропольского края «Ипатовская районная станция по борьбе с болезнями животных»</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="10" t="n">
+        <v>46321.5</v>
+      </c>
+      <c r="K72" s="8" t="inlineStr"/>
+      <c r="L72" s="8" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
+      <c r="N72" s="6" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>0331200023026000272</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для клинико-диагностической лаборатории (пробирки)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Здравоохранения Воронежской обл. «Областная Детская Клиническая Больница № 2»</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>36 Воронежская область</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="10" t="n">
+        <v>46316.6875</v>
+      </c>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>0303300007726000062</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ Республики Дагестан «Кумторкалинская Центральная Районная Больница»</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>05 Республика Дагестан</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="10" t="n">
+        <v>46316.33333333334</v>
+      </c>
+      <c r="K74" s="8" t="inlineStr"/>
+      <c r="L74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
+      <c r="N74" s="6" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>0318300169226000226</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Приморско-Ахтарская Центральная Районная Больница Имени Кравченко Н.Г.» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="10" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="K75" s="8" t="inlineStr"/>
+      <c r="L75" s="8" t="inlineStr"/>
+      <c r="M75" s="8" t="inlineStr"/>
+      <c r="N75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>0387200003226000356</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для микробиологической лаборатории</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Сургутская Клиническая Травматологическая Больница»</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="10" t="n">
+        <v>46318.33333333334</v>
+      </c>
+      <c r="K76" s="8" t="inlineStr"/>
+      <c r="L76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
+      <c r="N76" s="6" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>10763551</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>На поставку изделий медицинского назначения (Контейнер для сбора проб мочи ИВД)</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Калининградской обл. «Городская больница № 2»</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="10" t="n">
+        <v>46316.59583333333</v>
+      </c>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="inlineStr"/>
+      <c r="N77" s="6" t="n"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>0322300036726000232</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Поставка пробирок вакуумных</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Краевое ГБУЗ «Городская Поликлиника Железнодорожного Района» Министерства Здравоохранения Хабаровского Края</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>27 Хабаровский край</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="n"/>
+      <c r="J78" s="10" t="n">
+        <v>46315.45833333334</v>
+      </c>
+      <c r="K78" s="8" t="inlineStr"/>
+      <c r="L78" s="8" t="inlineStr"/>
+      <c r="M78" s="8" t="inlineStr"/>
+      <c r="N78" s="6" t="n"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>0317200016526000435</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Краевое ГБУЗ «Консультативно-Диагностический Центр Алтайского Края»</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>22 Алтайский край</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="10" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="8" t="inlineStr"/>
+      <c r="M79" s="8" t="inlineStr"/>
+      <c r="N79" s="6" t="n"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>0343200023226000185</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>на поставку медицинских изделий</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>ГБУ «Курганский Областной Кардиологический Диспансер»</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>45 Курганская область</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="10" t="n">
+        <v>46321.41666666666</v>
+      </c>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr"/>
+      <c r="N80" s="6" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>0321200014126000207</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов венозной крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Ставропольского Края «Ставропольский Краевой Клинический Онкологический Диспансер»</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>26 Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="10" t="n">
+        <v>46316.66666666666</v>
+      </c>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
+      <c r="N81" s="6" t="n"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>0318300169226000227</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Пробирка вакуумная для взятия образцов крови ИВД, с K2ЭДТА</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Приморско-Ахтарская Центральная Районная Больница Имени Кравченко Н.Г.» Министерства Здравоохранения Краснодарского Края</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>23 Краснодарский край</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="10" t="n">
+        <v>46316.625</v>
+      </c>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="6" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>0335300052226000348</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>На поставку изделий медицинского назначения контейнер (для сбора проб мочи ИВД)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Калининградской обл. «Городская Больница № 2»</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>39 Калининградская область</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="n"/>
+      <c r="J83" s="10" t="n">
+        <v>46326.75</v>
+      </c>
+      <c r="K83" s="8" t="inlineStr"/>
+      <c r="L83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
+      <c r="N83" s="6" t="n"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>17414</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>[ЗНЗ №44805]Специнвентарь</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>АО «Свинокомплекс «Устьволмский»</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>53 Новгородская область</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП STI-Trade</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="10" t="n">
+        <v>46322.66666666666</v>
+      </c>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="6" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>10761405</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинского расходного материала</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Нижневартовская Психоневрологическая Больница»</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="10" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="inlineStr"/>
+      <c r="M85" s="8" t="inlineStr"/>
+      <c r="N85" s="6" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>0367200003426000271</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских изделий: Контейнер для сбора проб мокроты ИВД</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Тюменской обл. «Областной Клинический Фтизиопульмонологический Центр»</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>72 Тюменская область</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="n"/>
+      <c r="J86" s="10" t="n">
+        <v>46325.58333333334</v>
+      </c>
+      <c r="K86" s="8" t="inlineStr"/>
+      <c r="L86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="6" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>6249850</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинского расходного материала</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Нижневартовская Психоневрологическая Больница»</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Малые закупки</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>Малая закупка</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Портал поставщиков</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="10" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="K87" s="8" t="inlineStr"/>
+      <c r="L87" s="8" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
+      <c r="N87" s="6" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>0351200001926000075</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинского расходного материала для анализатора газов крови «Radiometer» ABL 800</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>ГБУЗ Новосибирской обл. «Новосибирский Областной Клинический Кардиологический Диспансер»</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>54 Новосибирская область</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="10" t="n">
+        <v>46318.20833333334</v>
+      </c>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="6" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>0387200005526000172</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Поставка медицинских реагентов для анализатора электролитов EASYLYTE LITHIUM (имеющегося в наличии у заказчика)</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономного Округа - Югры «Сургутская Клиническая Психоневрологическая Больница»</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>86 Ханты-Мансийский АО (Югра)</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="10" t="n">
+        <v>46316.66666666666</v>
+      </c>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="8" t="inlineStr"/>
+      <c r="M89" s="8" t="inlineStr"/>
+      <c r="N89" s="6" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>4633931</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Запчасти для лабораторного оборудования</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>АО «СибИАЦ»</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>42 Кемеровская область</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="10" t="n">
+        <v>46322.25</v>
+      </c>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="6" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>76-ТМЦ</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Выбор поставщика на комплексное материально-техническое оснащение дошкольной образовательной организации (ДОО) на территории жилого комплекса "Ультима Сити".</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Рсг - Бизнес Сервис»</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>Кортрос</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="10" t="n">
+        <v>46323.66666666666</v>
+      </c>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="6" t="n"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>385-279</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Сервис по обеспечению канцелярскими, хозяйственными и расходными материалами Ozon</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Интернет Решения»</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="10" t="n">
+        <v>46321.54166666666</v>
+      </c>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="6" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>3506557</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Поставка ТМЦ АХН (товарно-материальных ценностей административно-хозяйственного назначения) для нужд АО «Росатом Возобновляемая энергия» (Регионы)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>АО «Росатом Возобновляемая Энергия»</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Мониторинг цен</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП «Фабрикант»</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="10" t="n">
+        <v>46323.99930555555</v>
+      </c>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="inlineStr"/>
+      <c r="M93" s="8" t="inlineStr"/>
+      <c r="N93" s="6" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>4582720</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Канцелярские товары - АО "СибЭР" - Кузбасс</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>АО «Сибэр»</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>24 Красноярский край</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="10" t="n">
+        <v>46317.5</v>
+      </c>
+      <c r="K94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="6" t="n"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>4645320</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Закупка по категории - канцелярские и хозяйственные товары</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>ПАО «Корпорация Всмпо-Ависма»</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>66 Свердловская область</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="n"/>
+      <c r="J95" s="10" t="n">
+        <v>46318.625</v>
+      </c>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+      <c r="N95" s="6" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>385-381</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Запрос котировок на поставку запчастей для оборудования, инструментов, смазочных материалов, лакокрасочных материалов, хоз и канцтоваров (офисная бумага, туалетная бумага, бытовая химия, инвентарь и т.д.), тары и упаковки, расходных и крепёжные материалов, СИЗ и спецодежды, оборудования и мебели (NZAK-2622)</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>ООО «О2о Холдинг»</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="10" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+      <c r="N96" s="6" t="n"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>1025385</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Разовая поставка канцелярских товаров</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>ООО «Миртелеком»</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>91 Республика Крым</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>Запрос цен</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>ЭТП ГПБ</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="n"/>
+      <c r="J97" s="10" t="n">
+        <v>46317.625</v>
+      </c>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
+      <c r="N97" s="6" t="n"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>4619514</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>ТОАЗ-009010 ЭПБ тех. устройств. 2027г.</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>АО «Тоаз»</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>63 Самарская область</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>Процедура закупки</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="10" t="n">
+        <v>46316.5</v>
+      </c>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
+      <c r="N98" s="6" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>249682</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Поставка лаб. посуды с фикс-й цены на 2027-28 г. для ГК "ФОСАГРО"</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>ПАО «Фосагро»</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>77 Москва</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Коммерческие</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Тендер</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>ФосАгро</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="n"/>
+      <c r="J99" s="10" t="n">
+        <v>46335.5625</v>
+      </c>
+      <c r="K99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr"/>
+      <c r="M99" s="8" t="inlineStr"/>
+      <c r="N99" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N99"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5924,7 +11246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6570,13 +11892,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7911,110 +13233,14 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="6" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>4645320</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Закупка по категории - канцелярские и хозяйственные товары</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>ПАО «Корпорация Всмпо-Ависма»</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>66 Свердловская область</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Запрос предложений</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="10" t="n">
-        <v>46318.625</v>
-      </c>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
-      <c r="N27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>76-ТМЦ</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Выбор поставщика на комплексное материально-техническое оснащение дошкольной образовательной организации (ДОО) на территории жилого комплекса "Ультима Сити".</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>ООО «Рсг - Бизнес Сервис»</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>77 Москва</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Тендер</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Кортрос</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="10" t="n">
-        <v>46323.66666666666</v>
-      </c>
-      <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr"/>
-      <c r="N28" s="6" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N28"/>
+  <autoFilter ref="A1:N26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8652,7 +13878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12000,7 +17226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13194,7 +18420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13780,252 +19006,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Номер закупки</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Предмет</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Регион</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Закон</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Способ</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Площадка</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>НМЦК, ₽</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Окончание подачи</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>СМП</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Обеспечение заявки</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Обеспечение контракта</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Аванс</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>386-176</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Поставка фильтров (абсолютной очистки, карманных), отсрочка 60 календарных дней, Российская Федерация, Новосибирская область, муниципальный округ Маслянинский, квартал Молочный, земельный участок 1.</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>ООО «ЭкоНива-Семена»</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>36 Воронежская область</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Тендер</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Bidzaar</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="n">
-        <v>46315.5</v>
-      </c>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="8" t="inlineStr"/>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>0321500000226000310</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>поставка товара для обеспечения нужд Ставропольского края</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>ГБУЗ Ставропольского Края «Ставропольский Краевой Клинический Перинатальный Центр № 1»</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>26 Ставропольский край</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>44-ФЗ</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Запрос цен</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="n">
-        <v>46318.79166666666</v>
-      </c>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>4646700</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Поставка фильтров (топливных, воздушных, масляных)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>ООО «Лукойл-Транс»</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>77 Москва</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Запрос предложений</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="10" t="n">
-        <v>46332.5</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:N4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>